--- a/results/0916-all/青藏高寒牧区/tech_selected_summary.xlsx
+++ b/results/0916-all/青藏高寒牧区/tech_selected_summary.xlsx
@@ -139,28 +139,28 @@
     <t>仲巴县</t>
   </si>
   <si>
-    <t>县名</t>
-  </si>
-  <si>
-    <t>技术1</t>
-  </si>
-  <si>
-    <t>总经济成本</t>
+    <t>Counties</t>
+  </si>
+  <si>
+    <t>Tech1</t>
+  </si>
+  <si>
+    <t>Total economic cost</t>
   </si>
   <si>
     <t>Feed processing_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 1617936.60</t>
-  </si>
-  <si>
-    <t>总经济成本: 0.00</t>
+    <t>1617936.60</t>
+  </si>
+  <si>
+    <t>0.00</t>
   </si>
   <si>
     <t>By-products source_sheep &amp; goat</t>
   </si>
   <si>
-    <t>总经济成本: 11407330.00</t>
+    <t>11407330.00</t>
   </si>
 </sst>
 </file>
